--- a/Tableur conso composants.xlsx
+++ b/Tableur conso composants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mod_loc\Documents\Anael\2025-2026\PROJET 2026 PICO-CENTRALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCB1640-1D96-46A6-B552-F677DA7BC615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F6FC3D-D628-4A5D-B49D-3E5B4A751576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="19440" windowHeight="14880" xr2:uid="{5D46380C-3031-486A-B8DE-7C3B63BDF9C7}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="19440" windowHeight="15600" xr2:uid="{5D46380C-3031-486A-B8DE-7C3B63BDF9C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>Appareil</t>
   </si>
@@ -132,6 +132,24 @@
   </si>
   <si>
     <t>0,008A</t>
+  </si>
+  <si>
+    <t>Ultrason</t>
+  </si>
+  <si>
+    <t>16mA</t>
+  </si>
+  <si>
+    <t>3mA</t>
+  </si>
+  <si>
+    <t>3V3</t>
+  </si>
+  <si>
+    <t>15mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300mA </t>
   </si>
 </sst>
 </file>
@@ -1761,6 +1779,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE5282FC-74E7-457C-BF37-34AF7C89EF57}">
   <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1796,7 +1817,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -1824,9 +1845,6 @@
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
@@ -1943,6 +1961,15 @@
       <c r="A9" t="s">
         <v>14</v>
       </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
@@ -1960,6 +1987,9 @@
       <c r="A10" t="s">
         <v>15</v>
       </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
@@ -1983,6 +2013,9 @@
       <c r="A11" t="s">
         <v>17</v>
       </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
@@ -2003,6 +2036,18 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
       <c r="H12">
         <v>4</v>
       </c>
